--- a/2026/BELTRAN 34/Julio/Julio BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Julio/Julio BELTRAN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELTRAN 34\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9D2C5E-B9E6-4E1F-88F4-EDDC1CC31F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6E8E38-091E-44E0-99C6-FEC1E442C62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$94</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$93</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="132">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -388,24 +393,9 @@
     <t>Pendiente para el cierre de Juni0 poner un AYSA de 418.590,24</t>
   </si>
   <si>
-    <t>Debito 03/06</t>
-  </si>
-  <si>
-    <t>Transf 05/06</t>
-  </si>
-  <si>
     <t>A SUBIR EN JUL10 - ESTAMOS COBRANDO $85,000 X MES</t>
   </si>
   <si>
-    <t>Mes de JUNIO</t>
-  </si>
-  <si>
-    <t>Envio cartas de documento correo argentino</t>
-  </si>
-  <si>
-    <t>Sra abogada Carina Gabriela Iconomopulos Cartas documento</t>
-  </si>
-  <si>
     <t>Mantenimiento de cuenta</t>
   </si>
   <si>
@@ -415,12 +405,6 @@
     <t>VTO 17/08</t>
   </si>
   <si>
-    <t>Mes de JULIO</t>
-  </si>
-  <si>
-    <t>Casa Ruan - Compra de materiales electricos</t>
-  </si>
-  <si>
     <t>Ascensores Contessi - Provision y cambio de boton exterior PB - Provision y cambio de display al indicador de cabina del ascensor</t>
   </si>
   <si>
@@ -431,6 +415,21 @@
   </si>
   <si>
     <t>Transf 06/07</t>
+  </si>
+  <si>
+    <t>Transf 02/07</t>
+  </si>
+  <si>
+    <t>Debito 03/07</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Casa Ruan - Compra de materiales electricos - Luces de emergencia</t>
+  </si>
+  <si>
+    <t>Transferencia identificada  1C</t>
   </si>
 </sst>
 </file>
@@ -750,7 +749,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -955,12 +954,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="39">
     <border>
@@ -1471,7 +1464,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1664,9 +1657,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="17" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1674,22 +1665,20 @@
     <xf numFmtId="44" fontId="42" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="43" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1708,6 +1697,54 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1717,56 +1754,11 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -1876,9 +1868,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1916,9 +1908,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1951,9 +1943,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1986,9 +1995,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2162,17 +2188,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L94"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L93"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2191,7 +2217,7 @@
       <c r="C2" s="77"/>
       <c r="D2" s="77"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1">
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
       <c r="A3" s="77" t="s">
         <v>64</v>
       </c>
@@ -2200,74 +2226,74 @@
       <c r="D3" s="77"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="159" t="s">
+      <c r="A4" s="157" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="159"/>
+      <c r="B4" s="157"/>
       <c r="C4" s="78"/>
       <c r="D4" s="78"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="159"/>
-      <c r="B5" s="159"/>
+      <c r="A5" s="157"/>
+      <c r="B5" s="157"/>
       <c r="C5" s="78"/>
       <c r="D5" s="78"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="159"/>
-      <c r="B6" s="159"/>
+      <c r="A6" s="157"/>
+      <c r="B6" s="157"/>
       <c r="C6" s="78"/>
       <c r="D6" s="78"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="159"/>
+      <c r="A7" s="157"/>
+      <c r="B7" s="157"/>
       <c r="C7" s="78"/>
       <c r="D7" s="78"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="167" t="s">
-        <v>127</v>
+      <c r="B9" s="165" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="167"/>
+      <c r="B10" s="165"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="167"/>
+      <c r="B11" s="165"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="162" t="s">
+      <c r="A14" s="160" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="162"/>
-      <c r="C14" s="162"/>
-      <c r="D14" s="162"/>
+      <c r="B14" s="160"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="160"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="162"/>
-      <c r="B15" s="162"/>
-      <c r="C15" s="162"/>
-      <c r="D15" s="162"/>
+      <c r="A15" s="160"/>
+      <c r="B15" s="160"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="160"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="162"/>
-      <c r="B16" s="162"/>
-      <c r="C16" s="162"/>
-      <c r="D16" s="162"/>
+      <c r="A16" s="160"/>
+      <c r="B16" s="160"/>
+      <c r="C16" s="160"/>
+      <c r="D16" s="160"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="162"/>
-      <c r="B17" s="162"/>
-      <c r="C17" s="162"/>
-      <c r="D17" s="162"/>
+      <c r="A17" s="160"/>
+      <c r="B17" s="160"/>
+      <c r="C17" s="160"/>
+      <c r="D17" s="160"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1"/>
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1"/>
     <row r="21" spans="1:7">
       <c r="A21" s="6" t="s">
         <v>21</v>
@@ -2290,23 +2316,17 @@
         <v>109</v>
       </c>
       <c r="B23" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="C23" s="147">
-        <v>270000</v>
+        <v>129</v>
+      </c>
+      <c r="C23" s="187">
+        <v>131000</v>
       </c>
       <c r="D23" s="54"/>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A24" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="147">
-        <v>261800</v>
-      </c>
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="146"/>
       <c r="D24" s="54"/>
     </row>
     <row r="25" spans="1:7">
@@ -2314,9 +2334,9 @@
         <v>48</v>
       </c>
       <c r="B25" s="117"/>
-      <c r="C25" s="151">
+      <c r="C25" s="149">
         <f>SUM(C23:C24)</f>
-        <v>531800</v>
+        <v>131000</v>
       </c>
       <c r="D25" s="55"/>
     </row>
@@ -2363,7 +2383,7 @@
       <c r="C31" s="10"/>
       <c r="D31" s="56">
         <f>C25+C30</f>
-        <v>531800</v>
+        <v>131000</v>
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
@@ -2379,24 +2399,24 @@
     </row>
     <row r="33" spans="1:7" ht="22.5" customHeight="1">
       <c r="A33" s="103" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B33" s="119"/>
-      <c r="C33" s="188">
+      <c r="C33" s="156">
         <v>85000</v>
       </c>
       <c r="D33" s="88"/>
       <c r="F33" s="22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1">
+    <row r="34" spans="1:7" ht="15.75" thickBot="1">
       <c r="A34" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="14"/>
-      <c r="C34" s="152"/>
+      <c r="C34" s="150"/>
       <c r="D34" s="56">
         <f>SUM(C33:C33)</f>
         <v>85000</v>
@@ -2411,18 +2431,18 @@
       <c r="D35" s="33"/>
     </row>
     <row r="36" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A36" s="160" t="s">
+      <c r="A36" s="158" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="161"/>
-      <c r="C36" s="148">
-        <v>168183</v>
+      <c r="B36" s="159"/>
+      <c r="C36" s="186">
+        <v>183061</v>
       </c>
       <c r="D36" s="87" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" thickBot="1">
       <c r="A37" s="14" t="s">
         <v>1</v>
       </c>
@@ -2430,7 +2450,7 @@
       <c r="C37" s="19"/>
       <c r="D37" s="58">
         <f>SUM(C36:C36)</f>
-        <v>168183</v>
+        <v>183061</v>
       </c>
     </row>
     <row r="38" spans="1:7" hidden="1">
@@ -2506,11 +2526,11 @@
         <v>95</v>
       </c>
       <c r="B45" s="54"/>
-      <c r="C45" s="93">
-        <v>51605.26</v>
+      <c r="C45" s="155">
+        <v>66292.55</v>
       </c>
       <c r="D45" s="85" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1">
@@ -2518,17 +2538,17 @@
         <v>96</v>
       </c>
       <c r="B46" s="54"/>
-      <c r="C46" s="187">
+      <c r="C46" s="155">
         <v>392672.62</v>
       </c>
       <c r="D46" s="85" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F46" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1">
+    <row r="47" spans="1:7" ht="15.75" thickBot="1">
       <c r="A47" s="14" t="s">
         <v>3</v>
       </c>
@@ -2536,10 +2556,10 @@
       <c r="C47" s="19"/>
       <c r="D47" s="58">
         <f>SUM(C45:C46)</f>
-        <v>444277.88</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1">
+        <v>458965.17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" thickBot="1">
       <c r="A48" s="13" t="s">
         <v>31</v>
       </c>
@@ -2547,41 +2567,41 @@
       <c r="C48" s="19"/>
       <c r="D48" s="61"/>
     </row>
-    <row r="49" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A49" s="160" t="s">
+    <row r="49" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A49" s="158" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="161"/>
-      <c r="C49" s="187">
+      <c r="B49" s="159"/>
+      <c r="C49" s="155">
         <v>126000</v>
       </c>
       <c r="D49" s="83" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="19.95" customHeight="1">
-      <c r="A50" s="156" t="s">
-        <v>129</v>
-      </c>
-      <c r="B50" s="157"/>
-      <c r="C50" s="187">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A50" s="185" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" s="154"/>
+      <c r="C50" s="155">
         <v>174000</v>
       </c>
       <c r="D50" s="83"/>
     </row>
     <row r="51" spans="1:6" ht="42.6" customHeight="1">
-      <c r="A51" s="160" t="s">
-        <v>130</v>
-      </c>
-      <c r="B51" s="161"/>
-      <c r="C51" s="187">
+      <c r="A51" s="158" t="s">
+        <v>123</v>
+      </c>
+      <c r="B51" s="159"/>
+      <c r="C51" s="155">
         <v>245000</v>
       </c>
       <c r="D51" s="83" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" thickBot="1">
       <c r="A52" s="14" t="s">
         <v>11</v>
       </c>
@@ -2592,7 +2612,7 @@
         <v>545000</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1">
+    <row r="53" spans="1:6" ht="15.75" thickBot="1">
       <c r="A53" s="13" t="s">
         <v>24</v>
       </c>
@@ -2602,7 +2622,7 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="54" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B54" s="54"/>
       <c r="C54" s="93">
@@ -2620,7 +2640,7 @@
       </c>
       <c r="D55" s="62"/>
     </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1">
+    <row r="56" spans="1:6" ht="15.75" thickBot="1">
       <c r="A56" s="122" t="s">
         <v>29</v>
       </c>
@@ -2631,28 +2651,28 @@
         <v>119418.48000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1">
+    <row r="57" spans="1:6" ht="15.75" thickBot="1">
       <c r="A57" s="54"/>
       <c r="B57" s="54"/>
       <c r="C57" s="54"/>
       <c r="D57" s="66"/>
     </row>
     <row r="58" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A58" s="164" t="s">
+      <c r="A58" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="165"/>
-      <c r="C58" s="166"/>
+      <c r="B58" s="163"/>
+      <c r="C58" s="164"/>
       <c r="D58" s="67"/>
     </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1">
+    <row r="59" spans="1:6" ht="15.75" thickBot="1">
       <c r="A59" s="123"/>
       <c r="B59" s="68"/>
       <c r="C59" s="68"/>
       <c r="D59" s="69"/>
       <c r="E59" s="24"/>
     </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1">
+    <row r="60" spans="1:6" ht="15.75" thickBot="1">
       <c r="A60" s="124" t="s">
         <v>25</v>
       </c>
@@ -2660,7 +2680,7 @@
       <c r="C60" s="70"/>
       <c r="D60" s="71">
         <f>(SUM(D26:D58))</f>
-        <v>1893679.3599999999</v>
+        <v>1522444.65</v>
       </c>
       <c r="E60" s="24"/>
       <c r="F60" s="24"/>
@@ -2672,7 +2692,7 @@
       <c r="D61" s="68"/>
       <c r="F61" s="82"/>
     </row>
-    <row r="62" spans="1:6" ht="15" thickBot="1">
+    <row r="62" spans="1:6" ht="15.75" thickBot="1">
       <c r="A62" s="68"/>
       <c r="B62" s="68"/>
       <c r="C62" s="68"/>
@@ -2723,12 +2743,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15" thickBot="1">
+    <row r="69" spans="1:4" ht="15.75" thickBot="1">
       <c r="A69" s="68"/>
       <c r="B69" s="68"/>
       <c r="C69" s="68"/>
     </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1">
+    <row r="70" spans="1:4" ht="15.75" thickBot="1">
       <c r="A70" s="124" t="s">
         <v>36</v>
       </c>
@@ -2739,32 +2759,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15" thickBot="1">
+    <row r="71" spans="1:4" ht="15.75" thickBot="1">
       <c r="A71" s="68"/>
       <c r="B71" s="68"/>
       <c r="C71" s="68"/>
     </row>
-    <row r="72" spans="1:4" ht="15" thickBot="1">
+    <row r="72" spans="1:4" ht="15.75" thickBot="1">
       <c r="A72" s="136" t="s">
         <v>26</v>
       </c>
       <c r="B72" s="137">
         <f>D60</f>
-        <v>1893679.3599999999</v>
+        <v>1522444.65</v>
       </c>
       <c r="C72" s="138"/>
     </row>
-    <row r="73" spans="1:4" ht="15" thickBot="1">
+    <row r="73" spans="1:4" ht="15.75" thickBot="1">
       <c r="A73" s="136" t="s">
         <v>27</v>
       </c>
       <c r="B73" s="137">
         <f>D60-D58</f>
-        <v>1893679.3599999999</v>
+        <v>1522444.65</v>
       </c>
       <c r="C73" s="68"/>
     </row>
-    <row r="74" spans="1:4" ht="15" thickBot="1">
+    <row r="74" spans="1:4" ht="15.75" thickBot="1">
       <c r="A74" s="136" t="s">
         <v>37</v>
       </c>
@@ -2774,7 +2794,7 @@
       </c>
       <c r="C74" s="68"/>
     </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1">
+    <row r="75" spans="1:4" ht="15.75" thickBot="1">
       <c r="A75" s="136" t="s">
         <v>52</v>
       </c>
@@ -2802,7 +2822,7 @@
       <c r="B78" s="68"/>
       <c r="C78" s="68"/>
     </row>
-    <row r="79" spans="1:4" ht="15" thickBot="1">
+    <row r="79" spans="1:4" ht="15.75" thickBot="1">
       <c r="A79" s="139" t="s">
         <v>47</v>
       </c>
@@ -2824,7 +2844,7 @@
       </c>
       <c r="B81" s="62">
         <f>PRORRATEO!H24</f>
-        <v>2668586.7200000002</v>
+        <v>1316307.9899999998</v>
       </c>
       <c r="C81" s="68"/>
     </row>
@@ -2833,101 +2853,91 @@
         <v>54</v>
       </c>
       <c r="B82" s="62">
-        <f>B93</f>
+        <f>B92</f>
         <v>0</v>
       </c>
       <c r="C82" s="68"/>
     </row>
-    <row r="83" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A83" s="143" t="s">
-        <v>124</v>
-      </c>
-      <c r="B83" s="153">
-        <v>-100000</v>
+    <row r="83" spans="1:12" ht="14.25" customHeight="1">
+      <c r="A83" s="142" t="s">
+        <v>131</v>
+      </c>
+      <c r="B83" s="151">
+        <v>-157200</v>
       </c>
       <c r="C83" s="68"/>
     </row>
-    <row r="84" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A84" s="142" t="s">
-        <v>123</v>
-      </c>
-      <c r="B84" s="153">
-        <f>--24000*2</f>
-        <v>48000</v>
+    <row r="84" spans="1:12">
+      <c r="A84" s="144" t="s">
+        <v>38</v>
+      </c>
+      <c r="B84" s="151">
+        <f>-B73</f>
+        <v>-1522444.65</v>
       </c>
       <c r="C84" s="68"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="144" t="s">
-        <v>38</v>
-      </c>
-      <c r="B85" s="153">
-        <f>-B73</f>
-        <v>-1893679.3599999999</v>
+      <c r="A85" s="143" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" s="62">
+        <f>-(B74)</f>
+        <v>0</v>
       </c>
       <c r="C85" s="68"/>
     </row>
     <row r="86" spans="1:12">
-      <c r="A86" s="143" t="s">
-        <v>39</v>
-      </c>
-      <c r="B86" s="62">
-        <f>-(B74)</f>
-        <v>0</v>
-      </c>
-      <c r="C86" s="68"/>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="A87" s="11" t="s">
+      <c r="A86" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B87" s="104">
-        <f>SUM(B80:B86)</f>
-        <v>976654.69</v>
-      </c>
-      <c r="C87" s="129"/>
-    </row>
-    <row r="88" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B88" s="22"/>
-      <c r="C88" s="24"/>
-      <c r="D88" s="129"/>
-    </row>
-    <row r="89" spans="1:12">
-      <c r="A89" s="163" t="s">
+      <c r="B86" s="104">
+        <f>SUM(B80:B85)</f>
+        <v>-109589.33000000077</v>
+      </c>
+      <c r="C86" s="129"/>
+    </row>
+    <row r="87" spans="1:12" ht="34.5" customHeight="1">
+      <c r="B87" s="22"/>
+      <c r="C87" s="24"/>
+      <c r="D87" s="129"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="161" t="s">
         <v>46</v>
       </c>
-      <c r="B89" s="163"/>
-    </row>
-    <row r="90" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A90" s="163"/>
-      <c r="B90" s="163"/>
+      <c r="B88" s="161"/>
+    </row>
+    <row r="89" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A89" s="161"/>
+      <c r="B89" s="161"/>
+    </row>
+    <row r="90" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A90" s="74"/>
+      <c r="B90" s="18"/>
     </row>
     <row r="91" spans="1:12" ht="32.25" customHeight="1">
       <c r="A91" s="74"/>
       <c r="B91" s="18"/>
     </row>
-    <row r="92" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A92" s="74"/>
-      <c r="B92" s="18"/>
+    <row r="92" spans="1:12">
+      <c r="A92" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="75">
+        <f>SUM(B90:B91)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="93" spans="1:12">
-      <c r="A93" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B93" s="75">
-        <f>SUM(B91:B92)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12">
-      <c r="L94" s="4"/>
+      <c r="L93" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A89:B90"/>
+    <mergeCell ref="A88:B89"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A49:B49"/>
@@ -2942,48 +2952,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.9" customHeight="1">
+    <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="105"/>
-      <c r="B1" s="172" t="str">
+      <c r="B1" s="166" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
       <c r="L1" s="106"/>
       <c r="M1" s="106"/>
       <c r="N1" s="106"/>
@@ -2992,16 +3002,16 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="108"/>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="167"/>
+      <c r="F2" s="167"/>
+      <c r="G2" s="167"/>
+      <c r="H2" s="167"/>
+      <c r="I2" s="167"/>
+      <c r="J2" s="167"/>
+      <c r="K2" s="167"/>
       <c r="L2" s="109"/>
       <c r="M2" s="109" t="s">
         <v>4</v>
@@ -3018,51 +3028,51 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="111"/>
-      <c r="B3" s="174"/>
-      <c r="C3" s="174"/>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="174"/>
-      <c r="J3" s="174"/>
-      <c r="K3" s="174"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
+      <c r="G3" s="168"/>
+      <c r="H3" s="168"/>
+      <c r="I3" s="168"/>
+      <c r="J3" s="168"/>
+      <c r="K3" s="168"/>
       <c r="L3" s="112"/>
       <c r="M3" s="112" t="s">
         <v>56</v>
       </c>
       <c r="N3" s="113"/>
-      <c r="O3" s="149">
+      <c r="O3" s="147">
         <v>0</v>
       </c>
       <c r="P3" s="114"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="184" t="s">
+      <c r="B4" s="179" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="185"/>
-      <c r="N4" s="185"/>
-      <c r="O4" s="185"/>
-      <c r="P4" s="186"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="180"/>
+      <c r="E4" s="180"/>
+      <c r="F4" s="180"/>
+      <c r="G4" s="180"/>
+      <c r="H4" s="180"/>
+      <c r="I4" s="180"/>
+      <c r="J4" s="180"/>
+      <c r="K4" s="180"/>
+      <c r="L4" s="180"/>
+      <c r="M4" s="180"/>
+      <c r="N4" s="180"/>
+      <c r="O4" s="180"/>
+      <c r="P4" s="181"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="168" t="s">
+      <c r="A5" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="170" t="s">
+      <c r="B5" s="184" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="171" t="s">
@@ -3086,50 +3096,50 @@
       <c r="I5" s="171" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="180" t="s">
+      <c r="J5" s="175" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="178" t="s">
+      <c r="K5" s="173" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="178" t="s">
+      <c r="L5" s="173" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="178" t="s">
+      <c r="M5" s="173" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="182" t="s">
+      <c r="N5" s="177" t="s">
         <v>51</v>
       </c>
       <c r="O5" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="175" t="s">
+      <c r="P5" s="169" t="s">
         <v>49</v>
       </c>
       <c r="S5" s="24"/>
       <c r="T5" s="22"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="169"/>
-      <c r="B6" s="170"/>
+      <c r="A6" s="183"/>
+      <c r="B6" s="184"/>
       <c r="C6" s="171"/>
       <c r="D6" s="171"/>
-      <c r="E6" s="177"/>
+      <c r="E6" s="172"/>
       <c r="F6" s="171"/>
       <c r="G6" s="171"/>
       <c r="H6" s="171"/>
-      <c r="I6" s="177"/>
-      <c r="J6" s="181"/>
-      <c r="K6" s="179"/>
-      <c r="L6" s="178"/>
-      <c r="M6" s="179"/>
-      <c r="N6" s="183"/>
+      <c r="I6" s="172"/>
+      <c r="J6" s="176"/>
+      <c r="K6" s="174"/>
+      <c r="L6" s="173"/>
+      <c r="M6" s="174"/>
+      <c r="N6" s="178"/>
       <c r="O6" s="29" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="P6" s="175"/>
+      <c r="P6" s="169"/>
       <c r="S6" s="22">
         <v>65160</v>
       </c>
@@ -3159,17 +3169,17 @@
         <v>10.86</v>
       </c>
       <c r="G7" s="36">
-        <v>4573102.01</v>
-      </c>
-      <c r="H7" s="37"/>
+        <v>5037143.01</v>
+      </c>
+      <c r="H7" s="152"/>
       <c r="I7" s="38"/>
       <c r="J7" s="39">
         <f>G7-H7</f>
-        <v>4573102.01</v>
+        <v>5037143.01</v>
       </c>
       <c r="K7" s="39">
         <f>IF(J7&gt;0,J7*3%,0)</f>
-        <v>137193.06029999998</v>
+        <v>151114.29029999999</v>
       </c>
       <c r="L7" s="40">
         <f>O$3*F7%</f>
@@ -3184,11 +3194,11 @@
       </c>
       <c r="O7" s="42">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>5037143.01</v>
+        <v>5515105.0099999998</v>
       </c>
       <c r="P7" s="43">
         <f t="shared" ref="P7:P23" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>5188257.01</v>
+        <v>5680558.0099999998</v>
       </c>
       <c r="Q7" s="24">
         <v>0.01</v>
@@ -3205,7 +3215,7 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A8" s="155" t="s">
+      <c r="A8" s="153" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="84">
@@ -3222,20 +3232,17 @@
         <v>11.16</v>
       </c>
       <c r="G8" s="36">
-        <v>493952.02</v>
-      </c>
-      <c r="H8" s="37">
-        <f>304543+243209-H18</f>
-        <v>509905.88</v>
-      </c>
+        <v>167834.02</v>
+      </c>
+      <c r="H8" s="152"/>
       <c r="I8" s="38"/>
       <c r="J8" s="39">
         <f t="shared" ref="J8:J22" si="2">G8-H8</f>
-        <v>-15953.859999999986</v>
+        <v>167834.02</v>
       </c>
       <c r="K8" s="39">
         <f t="shared" ref="K8:K22" si="3">IF(J8&gt;0,J8*3%,0)</f>
-        <v>0</v>
+        <v>5035.0205999999998</v>
       </c>
       <c r="L8" s="40">
         <f t="shared" ref="L8:L23" si="4">O$3*F8%</f>
@@ -3250,11 +3257,11 @@
       </c>
       <c r="O8" s="42">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>167834.02</v>
+        <v>356657.02</v>
       </c>
       <c r="P8" s="43">
         <f t="shared" si="0"/>
-        <v>172869.02</v>
+        <v>367357.02</v>
       </c>
       <c r="Q8" s="24">
         <f>Q7+0.01</f>
@@ -3292,19 +3299,17 @@
         <v>6.95</v>
       </c>
       <c r="G9" s="37">
-        <v>501046.03</v>
-      </c>
-      <c r="H9" s="37">
-        <v>501000</v>
-      </c>
+        <v>114503.03</v>
+      </c>
+      <c r="H9" s="152"/>
       <c r="I9" s="38"/>
       <c r="J9" s="98">
         <f t="shared" si="2"/>
-        <v>46.03000000002794</v>
+        <v>114503.03</v>
       </c>
       <c r="K9" s="39">
         <f t="shared" si="3"/>
-        <v>1.3809000000008382</v>
+        <v>3435.0908999999997</v>
       </c>
       <c r="L9" s="99">
         <f t="shared" si="4"/>
@@ -3319,11 +3324,11 @@
       </c>
       <c r="O9" s="101">
         <f t="shared" ref="O9:O23" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>114503.03</v>
+        <v>232394.03</v>
       </c>
       <c r="P9" s="102">
         <f t="shared" si="0"/>
-        <v>117938.03</v>
+        <v>239366.03</v>
       </c>
       <c r="Q9" s="24">
         <f t="shared" ref="Q9:Q22" si="7">Q8+0.01</f>
@@ -3344,33 +3349,36 @@
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="158">
+      <c r="B10" s="84">
         <v>3</v>
       </c>
-      <c r="C10" s="158" t="s">
+      <c r="C10" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="158" t="s">
+      <c r="D10" s="84" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="158" t="s">
+      <c r="E10" s="84" t="s">
         <v>114</v>
       </c>
       <c r="F10" s="35">
         <v>7.37</v>
       </c>
       <c r="G10" s="36">
-        <v>183761.04</v>
-      </c>
-      <c r="H10" s="37"/>
+        <v>310647.03999999998</v>
+      </c>
+      <c r="H10" s="152">
+        <f>157200+129937-H20</f>
+        <v>265075.86</v>
+      </c>
       <c r="I10" s="38"/>
       <c r="J10" s="39">
         <f t="shared" si="2"/>
-        <v>183761.04</v>
+        <v>45571.179999999993</v>
       </c>
       <c r="K10" s="39">
         <f t="shared" si="3"/>
-        <v>5512.8311999999996</v>
+        <v>1367.1353999999997</v>
       </c>
       <c r="L10" s="40">
         <f t="shared" si="4"/>
@@ -3385,11 +3393,11 @@
       </c>
       <c r="O10" s="42">
         <f t="shared" si="6"/>
-        <v>310647.03999999998</v>
+        <v>168311.04000000001</v>
       </c>
       <c r="P10" s="43">
         <f t="shared" si="0"/>
-        <v>319966.03999999998</v>
+        <v>173360.04</v>
       </c>
       <c r="Q10" s="24">
         <f t="shared" si="7"/>
@@ -3406,7 +3414,7 @@
         <v>218940</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1">
+    <row r="11" spans="1:21" ht="27" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -3426,20 +3434,19 @@
         <v>10.68</v>
       </c>
       <c r="G11" s="36">
-        <v>269136.05</v>
-      </c>
-      <c r="H11" s="37">
-        <f>208794+60342</f>
-        <v>269136</v>
+        <v>175883.05</v>
+      </c>
+      <c r="H11" s="152">
+        <v>181159.05</v>
       </c>
       <c r="I11" s="38"/>
       <c r="J11" s="39">
         <f t="shared" si="2"/>
-        <v>4.9999999988358468E-2</v>
+        <v>-5276</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="3"/>
-        <v>1.499999999650754E-3</v>
+        <v>0</v>
       </c>
       <c r="L11" s="40">
         <f t="shared" si="4"/>
@@ -3454,11 +3461,11 @@
       </c>
       <c r="O11" s="42">
         <f t="shared" si="6"/>
-        <v>175883.05</v>
+        <v>170607.05</v>
       </c>
       <c r="P11" s="43">
         <f t="shared" si="0"/>
-        <v>181159.05</v>
+        <v>175725.05</v>
       </c>
       <c r="Q11" s="24">
         <f t="shared" si="7"/>
@@ -3495,16 +3502,16 @@
         <v>6.95</v>
       </c>
       <c r="G12" s="36">
-        <v>175139.06</v>
-      </c>
-      <c r="H12" s="37">
-        <f>190513-H22+42715</f>
-        <v>217855.84</v>
+        <v>71739.06</v>
+      </c>
+      <c r="H12" s="152">
+        <f>G12</f>
+        <v>71739.06</v>
       </c>
       <c r="I12" s="38"/>
       <c r="J12" s="39">
         <f t="shared" si="2"/>
-        <v>-42716.78</v>
+        <v>0</v>
       </c>
       <c r="K12" s="39">
         <f t="shared" si="3"/>
@@ -3523,11 +3530,11 @@
       </c>
       <c r="O12" s="42">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>71739.06</v>
+        <v>114456.06</v>
       </c>
       <c r="P12" s="43">
         <f t="shared" si="0"/>
-        <v>73891.06</v>
+        <v>117890.06</v>
       </c>
       <c r="Q12" s="24">
         <f t="shared" si="7"/>
@@ -3564,11 +3571,11 @@
         <v>6.89</v>
       </c>
       <c r="G13" s="36">
-        <v>173628.07</v>
-      </c>
-      <c r="H13" s="37">
+        <v>113468.07</v>
+      </c>
+      <c r="H13" s="152">
         <f>G13</f>
-        <v>173628.07</v>
+        <v>113468.07</v>
       </c>
       <c r="I13" s="38"/>
       <c r="J13" s="39">
@@ -3634,11 +3641,11 @@
         <v>10.68</v>
       </c>
       <c r="G14" s="36">
-        <v>269136.08</v>
-      </c>
-      <c r="H14" s="37">
+        <v>175883.08</v>
+      </c>
+      <c r="H14" s="152">
         <f>G14</f>
-        <v>269136.08</v>
+        <v>175883.08</v>
       </c>
       <c r="I14" s="38"/>
       <c r="J14" s="39">
@@ -3703,16 +3710,16 @@
         <v>6.95</v>
       </c>
       <c r="G15" s="37">
-        <v>175140.09</v>
-      </c>
-      <c r="H15" s="146">
-        <f>175140.09+39268.09</f>
-        <v>214408.18</v>
+        <v>75188.09</v>
+      </c>
+      <c r="H15" s="152">
+        <f>G15*2</f>
+        <v>150376.18</v>
       </c>
       <c r="I15" s="38"/>
       <c r="J15" s="98">
         <f t="shared" si="2"/>
-        <v>-39268.089999999997</v>
+        <v>-75188.09</v>
       </c>
       <c r="K15" s="98">
         <v>0</v>
@@ -3730,11 +3737,11 @@
       </c>
       <c r="O15" s="101">
         <f t="shared" si="6"/>
-        <v>75188.09</v>
+        <v>39268.089999999997</v>
       </c>
       <c r="P15" s="102">
         <f t="shared" si="0"/>
-        <v>77444.09</v>
+        <v>40446.089999999997</v>
       </c>
       <c r="Q15" s="24">
         <f t="shared" si="7"/>
@@ -3771,19 +3778,19 @@
         <v>6.89</v>
       </c>
       <c r="G16" s="36">
-        <v>173628.1</v>
-      </c>
-      <c r="H16" s="37">
-        <v>134700</v>
+        <v>153564.1</v>
+      </c>
+      <c r="H16" s="152">
+        <v>113468</v>
       </c>
       <c r="I16" s="38"/>
       <c r="J16" s="39">
         <f t="shared" si="2"/>
-        <v>38928.100000000006</v>
+        <v>40096.100000000006</v>
       </c>
       <c r="K16" s="39">
         <f t="shared" si="3"/>
-        <v>1167.8430000000001</v>
+        <v>1202.883</v>
       </c>
       <c r="L16" s="40">
         <f t="shared" si="4"/>
@@ -3798,11 +3805,11 @@
       </c>
       <c r="O16" s="42">
         <f t="shared" si="6"/>
-        <v>153564.1</v>
+        <v>154767.1</v>
       </c>
       <c r="P16" s="43">
         <f t="shared" si="0"/>
-        <v>158171.1</v>
+        <v>159410.1</v>
       </c>
       <c r="Q16" s="24">
         <f t="shared" si="7"/>
@@ -3840,11 +3847,11 @@
         <v>11.88</v>
       </c>
       <c r="G17" s="36">
-        <v>299686.11</v>
-      </c>
-      <c r="H17" s="37">
+        <v>195646.11</v>
+      </c>
+      <c r="H17" s="152">
         <f>G17</f>
-        <v>299686.11</v>
+        <v>195646.11</v>
       </c>
       <c r="I17" s="38"/>
       <c r="J17" s="39">
@@ -3910,20 +3917,17 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G18" s="36">
-        <v>37846.120000000003</v>
-      </c>
-      <c r="H18" s="37">
-        <f>G18</f>
-        <v>37846.120000000003</v>
-      </c>
+        <v>9387.1200000000008</v>
+      </c>
+      <c r="H18" s="152"/>
       <c r="I18" s="38"/>
       <c r="J18" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9387.1200000000008</v>
       </c>
       <c r="K18" s="39">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>281.61360000000002</v>
       </c>
       <c r="L18" s="40">
         <f t="shared" si="4"/>
@@ -3938,11 +3942,11 @@
       </c>
       <c r="O18" s="42">
         <f t="shared" si="6"/>
-        <v>9387.1200000000008</v>
+        <v>19056.12</v>
       </c>
       <c r="P18" s="43">
         <f t="shared" si="0"/>
-        <v>9669.1200000000008</v>
+        <v>19628.12</v>
       </c>
       <c r="Q18" s="24">
         <f t="shared" si="7"/>
@@ -3977,16 +3981,15 @@
         <v>0.52</v>
       </c>
       <c r="G19" s="36">
-        <v>12808.13</v>
-      </c>
-      <c r="H19" s="37">
-        <f>G19</f>
-        <v>12808.13</v>
+        <v>8564.1299999999992</v>
+      </c>
+      <c r="H19" s="152">
+        <v>8821.1299999999992</v>
       </c>
       <c r="I19" s="38"/>
       <c r="J19" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-257</v>
       </c>
       <c r="K19" s="39">
         <f t="shared" si="3"/>
@@ -4005,11 +4008,11 @@
       </c>
       <c r="O19" s="42">
         <f t="shared" si="6"/>
-        <v>8564.1299999999992</v>
+        <v>8307.1299999999992</v>
       </c>
       <c r="P19" s="43">
         <f t="shared" si="0"/>
-        <v>8821.1299999999992</v>
+        <v>8556.1299999999992</v>
       </c>
       <c r="Q19" s="24">
         <f t="shared" si="7"/>
@@ -4046,17 +4049,20 @@
         <v>0.52</v>
       </c>
       <c r="G20" s="36">
-        <v>13104.14</v>
-      </c>
-      <c r="H20" s="37"/>
+        <v>22061.14</v>
+      </c>
+      <c r="H20" s="152">
+        <f>G20</f>
+        <v>22061.14</v>
+      </c>
       <c r="I20" s="38"/>
       <c r="J20" s="39">
         <f t="shared" si="2"/>
-        <v>13104.14</v>
+        <v>0</v>
       </c>
       <c r="K20" s="39">
         <f t="shared" si="3"/>
-        <v>393.12419999999997</v>
+        <v>0</v>
       </c>
       <c r="L20" s="40">
         <f t="shared" si="4"/>
@@ -4071,11 +4077,11 @@
       </c>
       <c r="O20" s="42">
         <f t="shared" si="6"/>
-        <v>22061.14</v>
+        <v>8564.14</v>
       </c>
       <c r="P20" s="43">
         <f t="shared" si="0"/>
-        <v>22723.14</v>
+        <v>8821.14</v>
       </c>
       <c r="Q20" s="24">
         <f t="shared" si="7"/>
@@ -4110,11 +4116,11 @@
         <v>0.52</v>
       </c>
       <c r="G21" s="36">
-        <v>13104.15</v>
-      </c>
-      <c r="H21" s="37">
+        <v>8564.15</v>
+      </c>
+      <c r="H21" s="152">
         <f>G21</f>
-        <v>13104.15</v>
+        <v>8564.15</v>
       </c>
       <c r="I21" s="38"/>
       <c r="J21" s="39">
@@ -4177,11 +4183,11 @@
         <v>0.61</v>
       </c>
       <c r="G22" s="36">
-        <v>15372.16</v>
-      </c>
-      <c r="H22" s="154">
+        <v>10046.16</v>
+      </c>
+      <c r="H22" s="152">
         <f>G22</f>
-        <v>15372.16</v>
+        <v>10046.16</v>
       </c>
       <c r="I22" s="38"/>
       <c r="J22" s="39">
@@ -4274,11 +4280,11 @@
       </c>
       <c r="G24" s="27">
         <f>SUM(G7:G23)</f>
-        <v>7379589.3599999994</v>
+        <v>6650121.3599999994</v>
       </c>
       <c r="H24" s="30">
         <f>SUM(H7:H23)</f>
-        <v>2668586.7200000002</v>
+        <v>1316307.9899999998</v>
       </c>
       <c r="I24" s="30">
         <f>SUM(I7:I23)</f>
@@ -4300,11 +4306,11 @@
       </c>
       <c r="O24" s="53">
         <f>SUM(O7:O22)</f>
-        <v>6650121.3599999994</v>
+        <v>7291100.3599999994</v>
       </c>
       <c r="P24" s="53">
         <f>SUM(P7:P22)</f>
-        <v>6849623.3599999994</v>
+        <v>7509832.3599999994</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="12.75" customHeight="1">
@@ -4314,94 +4320,99 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="D27" s="176" t="s">
+      <c r="D27" s="170" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="176"/>
-      <c r="F27" s="176"/>
-      <c r="G27" s="176"/>
-      <c r="H27" s="176"/>
-      <c r="I27" s="176"/>
-      <c r="J27" s="176"/>
-      <c r="K27" s="176"/>
-      <c r="L27" s="176"/>
-      <c r="M27" s="176"/>
-      <c r="N27" s="176"/>
-      <c r="O27" s="176"/>
+      <c r="E27" s="170"/>
+      <c r="F27" s="170"/>
+      <c r="G27" s="170"/>
+      <c r="H27" s="170"/>
+      <c r="I27" s="170"/>
+      <c r="J27" s="170"/>
+      <c r="K27" s="170"/>
+      <c r="L27" s="170"/>
+      <c r="M27" s="170"/>
+      <c r="N27" s="170"/>
+      <c r="O27" s="170"/>
       <c r="S27" s="22"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="176"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
-      <c r="G28" s="176"/>
-      <c r="H28" s="176"/>
-      <c r="I28" s="176"/>
-      <c r="J28" s="176"/>
-      <c r="K28" s="176"/>
-      <c r="L28" s="176"/>
-      <c r="M28" s="176"/>
-      <c r="N28" s="176"/>
-      <c r="O28" s="176"/>
+      <c r="D28" s="170"/>
+      <c r="E28" s="170"/>
+      <c r="F28" s="170"/>
+      <c r="G28" s="170"/>
+      <c r="H28" s="170"/>
+      <c r="I28" s="170"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="170"/>
+      <c r="L28" s="170"/>
+      <c r="M28" s="170"/>
+      <c r="N28" s="170"/>
+      <c r="O28" s="170"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="176"/>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
-      <c r="G29" s="176"/>
-      <c r="H29" s="176"/>
-      <c r="I29" s="176"/>
-      <c r="J29" s="176"/>
-      <c r="K29" s="176"/>
-      <c r="L29" s="176"/>
-      <c r="M29" s="176"/>
-      <c r="N29" s="176"/>
-      <c r="O29" s="176"/>
+      <c r="D29" s="170"/>
+      <c r="E29" s="170"/>
+      <c r="F29" s="170"/>
+      <c r="G29" s="170"/>
+      <c r="H29" s="170"/>
+      <c r="I29" s="170"/>
+      <c r="J29" s="170"/>
+      <c r="K29" s="170"/>
+      <c r="L29" s="170"/>
+      <c r="M29" s="170"/>
+      <c r="N29" s="170"/>
+      <c r="O29" s="170"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="176"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="176"/>
-      <c r="G30" s="176"/>
-      <c r="H30" s="176"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="176"/>
-      <c r="K30" s="176"/>
-      <c r="L30" s="176"/>
-      <c r="M30" s="176"/>
-      <c r="N30" s="176"/>
-      <c r="O30" s="176"/>
+      <c r="D30" s="170"/>
+      <c r="E30" s="170"/>
+      <c r="F30" s="170"/>
+      <c r="G30" s="170"/>
+      <c r="H30" s="170"/>
+      <c r="I30" s="170"/>
+      <c r="J30" s="170"/>
+      <c r="K30" s="170"/>
+      <c r="L30" s="170"/>
+      <c r="M30" s="170"/>
+      <c r="N30" s="170"/>
+      <c r="O30" s="170"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="176"/>
-      <c r="E31" s="176"/>
-      <c r="F31" s="176"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="176"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="176"/>
-      <c r="K31" s="176"/>
-      <c r="L31" s="176"/>
-      <c r="M31" s="176"/>
-      <c r="N31" s="176"/>
-      <c r="O31" s="176"/>
+      <c r="D31" s="170"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="170"/>
+      <c r="H31" s="170"/>
+      <c r="I31" s="170"/>
+      <c r="J31" s="170"/>
+      <c r="K31" s="170"/>
+      <c r="L31" s="170"/>
+      <c r="M31" s="170"/>
+      <c r="N31" s="170"/>
+      <c r="O31" s="170"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="176"/>
-      <c r="E32" s="176"/>
-      <c r="F32" s="176"/>
-      <c r="G32" s="176"/>
-      <c r="H32" s="176"/>
-      <c r="I32" s="176"/>
-      <c r="J32" s="176"/>
-      <c r="K32" s="176"/>
-      <c r="L32" s="176"/>
-      <c r="M32" s="176"/>
-      <c r="N32" s="176"/>
-      <c r="O32" s="176"/>
+      <c r="D32" s="170"/>
+      <c r="E32" s="170"/>
+      <c r="F32" s="170"/>
+      <c r="G32" s="170"/>
+      <c r="H32" s="170"/>
+      <c r="I32" s="170"/>
+      <c r="J32" s="170"/>
+      <c r="K32" s="170"/>
+      <c r="L32" s="170"/>
+      <c r="M32" s="170"/>
+      <c r="N32" s="170"/>
+      <c r="O32" s="170"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4415,11 +4426,6 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
@@ -4429,11 +4435,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA3CC01E-5816-4D6D-A47C-EE31C4411A86}">
   <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="3:3">
-      <c r="C3" s="150" t="s">
-        <v>126</v>
+      <c r="C3" s="148" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/2026/BELTRAN 34/Julio/Julio BELTRAN.xlsx
+++ b/2026/BELTRAN 34/Julio/Julio BELTRAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELTRAN 34\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6E8E38-091E-44E0-99C6-FEC1E442C62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984FFDAF-1178-481F-844A-283B9C1D2FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$94</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="134">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -393,9 +393,6 @@
     <t>Pendiente para el cierre de Juni0 poner un AYSA de 418.590,24</t>
   </si>
   <si>
-    <t>A SUBIR EN JUL10 - ESTAMOS COBRANDO $85,000 X MES</t>
-  </si>
-  <si>
     <t>Mantenimiento de cuenta</t>
   </si>
   <si>
@@ -429,7 +426,16 @@
     <t>Casa Ruan - Compra de materiales electricos - Luces de emergencia</t>
   </si>
   <si>
-    <t>Transferencia identificada  1C</t>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Transf 03/07</t>
+  </si>
+  <si>
+    <t>Envio carta documento local - Correo argentino</t>
+  </si>
+  <si>
+    <t>Subido en Juli0 a $91.000</t>
   </si>
 </sst>
 </file>
@@ -1464,7 +1470,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1668,8 +1674,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1697,6 +1707,18 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1712,9 +1734,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1745,20 +1764,7 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2188,7 +2194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2253,7 +2259,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="165" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2316,9 +2322,9 @@
         <v>109</v>
       </c>
       <c r="B23" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" s="187">
+        <v>128</v>
+      </c>
+      <c r="C23" s="146">
         <v>131000</v>
       </c>
       <c r="D23" s="54"/>
@@ -2399,15 +2405,15 @@
     </row>
     <row r="33" spans="1:7" ht="22.5" customHeight="1">
       <c r="A33" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B33" s="119"/>
-      <c r="C33" s="156">
+      <c r="C33" s="90">
         <v>85000</v>
       </c>
       <c r="D33" s="88"/>
       <c r="F33" s="22" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G33" s="9"/>
     </row>
@@ -2435,11 +2441,11 @@
         <v>65</v>
       </c>
       <c r="B36" s="159"/>
-      <c r="C36" s="186">
+      <c r="C36" s="185">
         <v>183061</v>
       </c>
       <c r="D36" s="87" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" thickBot="1">
@@ -2526,11 +2532,11 @@
         <v>95</v>
       </c>
       <c r="B45" s="54"/>
-      <c r="C45" s="155">
+      <c r="C45" s="93">
         <v>66292.55</v>
       </c>
       <c r="D45" s="85" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1">
@@ -2538,11 +2544,11 @@
         <v>96</v>
       </c>
       <c r="B46" s="54"/>
-      <c r="C46" s="155">
+      <c r="C46" s="93">
         <v>392672.62</v>
       </c>
       <c r="D46" s="85" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F46" t="s">
         <v>118</v>
@@ -2572,376 +2578,391 @@
         <v>112</v>
       </c>
       <c r="B49" s="159"/>
-      <c r="C49" s="155">
+      <c r="C49" s="93">
         <v>126000</v>
       </c>
       <c r="D49" s="83" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="19.899999999999999" customHeight="1">
-      <c r="A50" s="185" t="s">
+      <c r="A50" s="156" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="154"/>
+      <c r="C50" s="93">
+        <v>174000</v>
+      </c>
+      <c r="D50" s="83"/>
+    </row>
+    <row r="51" spans="1:6" ht="19.899999999999999" customHeight="1">
+      <c r="A51" s="156" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="154"/>
-      <c r="C50" s="155">
-        <v>174000</v>
-      </c>
-      <c r="D50" s="83"/>
-    </row>
-    <row r="51" spans="1:6" ht="42.6" customHeight="1">
-      <c r="A51" s="158" t="s">
+      <c r="B51" s="155"/>
+      <c r="C51" s="93">
+        <v>15500</v>
+      </c>
+      <c r="D51" s="83" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="42.6" customHeight="1">
+      <c r="A52" s="158" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="159"/>
+      <c r="C52" s="93">
+        <v>245000</v>
+      </c>
+      <c r="D52" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="B51" s="159"/>
-      <c r="C51" s="155">
-        <v>245000</v>
-      </c>
-      <c r="D51" s="83" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A52" s="14" t="s">
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A53" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="63">
-        <f>SUM(C49:C51)</f>
-        <v>545000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="13" t="s">
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="63">
+        <f>SUM(C49:C52)</f>
+        <v>560500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A54" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B53" s="121"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="61"/>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="54" t="s">
-        <v>120</v>
-      </c>
-      <c r="B54" s="54"/>
-      <c r="C54" s="93">
-        <v>69000</v>
-      </c>
-      <c r="D54" s="64"/>
+      <c r="B54" s="121"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="61"/>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="54" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B55" s="54"/>
       <c r="C55" s="93">
-        <v>50418.48</v>
-      </c>
-      <c r="D55" s="62"/>
-    </row>
-    <row r="56" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A56" s="122" t="s">
+        <v>69000</v>
+      </c>
+      <c r="D55" s="64"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" s="54"/>
+      <c r="C56" s="93">
+        <v>40885.53</v>
+      </c>
+      <c r="D56" s="62"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A57" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="B56" s="122"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="58">
-        <f>SUM(C54:C55)</f>
-        <v>119418.48000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="54"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="54"/>
-      <c r="D57" s="66"/>
-    </row>
-    <row r="58" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A58" s="162" t="s">
+      <c r="B57" s="122"/>
+      <c r="C57" s="65"/>
+      <c r="D57" s="58">
+        <f>SUM(C55:C56)</f>
+        <v>109885.53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A58" s="54"/>
+      <c r="B58" s="54"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="66"/>
+    </row>
+    <row r="59" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A59" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="163"/>
-      <c r="C58" s="164"/>
-      <c r="D58" s="67"/>
-    </row>
-    <row r="59" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A59" s="123"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="68"/>
-      <c r="D59" s="69"/>
-      <c r="E59" s="24"/>
+      <c r="B59" s="163"/>
+      <c r="C59" s="164"/>
+      <c r="D59" s="67">
+        <f>1646848.23-1528411.7</f>
+        <v>118436.53000000003</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="124" t="s">
+      <c r="A60" s="123"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="68"/>
+      <c r="D60" s="69"/>
+      <c r="E60" s="24"/>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A61" s="124" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="125"/>
-      <c r="C60" s="70"/>
-      <c r="D60" s="71">
-        <f>(SUM(D26:D58))</f>
-        <v>1522444.65</v>
-      </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="68"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="68"/>
-      <c r="D61" s="68"/>
-      <c r="F61" s="82"/>
-    </row>
-    <row r="62" spans="1:6" ht="15.75" thickBot="1">
+      <c r="B61" s="125"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="71">
+        <f>(SUM(D26:D59))</f>
+        <v>1646848.23</v>
+      </c>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="68"/>
       <c r="B62" s="68"/>
       <c r="C62" s="68"/>
       <c r="D62" s="68"/>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="126" t="s">
+      <c r="F62" s="82"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A63" s="68"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="68"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="B63" s="127"/>
-      <c r="C63" s="72"/>
-      <c r="D63" s="73"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="130"/>
-      <c r="B64" s="131"/>
-      <c r="C64" s="93"/>
-      <c r="D64" s="60"/>
+      <c r="B64" s="127"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="73"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="122" t="s">
+      <c r="A65" s="130"/>
+      <c r="B65" s="131"/>
+      <c r="C65" s="93"/>
+      <c r="D65" s="60"/>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="B65" s="132"/>
-      <c r="C65" s="133"/>
-      <c r="D65" s="145">
-        <f>SUM(C64:C64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="15" customHeight="1">
-      <c r="A66" s="68"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-    </row>
-    <row r="67" spans="1:4" hidden="1">
+      <c r="B66" s="132"/>
+      <c r="C66" s="133"/>
+      <c r="D66" s="145">
+        <f>SUM(C65:C65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15" customHeight="1">
       <c r="A67" s="68"/>
       <c r="B67" s="68"/>
       <c r="C67" s="68"/>
     </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="134" t="s">
+    <row r="68" spans="1:4" hidden="1">
+      <c r="A68" s="68"/>
+      <c r="B68" s="68"/>
+      <c r="C68" s="68"/>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="134" t="s">
         <v>35</v>
       </c>
-      <c r="B68" s="134"/>
-      <c r="C68" s="135"/>
-      <c r="D68" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A69" s="68"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68"/>
+      <c r="B69" s="134"/>
+      <c r="C69" s="135"/>
+      <c r="D69" s="89">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A70" s="124" t="s">
+      <c r="A70" s="68"/>
+      <c r="B70" s="68"/>
+      <c r="C70" s="68"/>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A71" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="B70" s="125"/>
-      <c r="C70" s="70"/>
-      <c r="D70" s="34">
-        <f>D65+D68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A71" s="68"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="68"/>
+      <c r="B71" s="125"/>
+      <c r="C71" s="70"/>
+      <c r="D71" s="34">
+        <f>D66+D69</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A72" s="136" t="s">
-        <v>26</v>
-      </c>
-      <c r="B72" s="137">
-        <f>D60</f>
-        <v>1522444.65</v>
-      </c>
-      <c r="C72" s="138"/>
+      <c r="A72" s="68"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="68"/>
     </row>
     <row r="73" spans="1:4" ht="15.75" thickBot="1">
       <c r="A73" s="136" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B73" s="137">
-        <f>D60-D58</f>
-        <v>1522444.65</v>
-      </c>
-      <c r="C73" s="68"/>
+        <f>D61</f>
+        <v>1646848.23</v>
+      </c>
+      <c r="C73" s="138"/>
     </row>
     <row r="74" spans="1:4" ht="15.75" thickBot="1">
       <c r="A74" s="136" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B74" s="137">
-        <f>D70-D68</f>
-        <v>0</v>
+        <f>D61-D59</f>
+        <v>1528411.7</v>
       </c>
       <c r="C74" s="68"/>
     </row>
     <row r="75" spans="1:4" ht="15.75" thickBot="1">
       <c r="A75" s="136" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" s="137">
+        <f>D71-D69</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="68"/>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A76" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="B75" s="137">
-        <f>D70</f>
-        <v>0</v>
-      </c>
-      <c r="C75" s="68"/>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="68"/>
-      <c r="B76" s="68"/>
+      <c r="B76" s="137">
+        <f>D71</f>
+        <v>0</v>
+      </c>
       <c r="C76" s="68"/>
-      <c r="D76" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="68"/>
       <c r="B77" s="68"/>
       <c r="C77" s="68"/>
+      <c r="D77" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="68"/>
       <c r="B78" s="68"/>
       <c r="C78" s="68"/>
     </row>
-    <row r="79" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A79" s="139" t="s">
+    <row r="79" spans="1:4">
+      <c r="A79" s="68"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="68"/>
+    </row>
+    <row r="80" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A80" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="B79" s="140"/>
-      <c r="C79" s="68"/>
-    </row>
-    <row r="80" spans="1:4" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A80" s="12" t="s">
+      <c r="B80" s="140"/>
+      <c r="C80" s="68"/>
+    </row>
+    <row r="81" spans="1:12" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A81" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B80" s="141">
-        <v>253747.32999999938</v>
-      </c>
-      <c r="C80" s="68"/>
-    </row>
-    <row r="81" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A81" s="142" t="s">
-        <v>55</v>
-      </c>
-      <c r="B81" s="62">
-        <f>PRORRATEO!H24</f>
-        <v>1316307.9899999998</v>
+      <c r="B81" s="141">
+        <v>1223485.8199999998</v>
       </c>
       <c r="C81" s="68"/>
     </row>
     <row r="82" spans="1:12" ht="14.25" customHeight="1">
       <c r="A82" s="142" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B82" s="62">
-        <f>B92</f>
-        <v>0</v>
+        <f>PRORRATEO!H24</f>
+        <v>1498846.13</v>
       </c>
       <c r="C82" s="68"/>
     </row>
     <row r="83" spans="1:12" ht="14.25" customHeight="1">
       <c r="A83" s="142" t="s">
-        <v>131</v>
-      </c>
-      <c r="B83" s="151">
-        <v>-157200</v>
+        <v>54</v>
+      </c>
+      <c r="B83" s="62">
+        <f>B93</f>
+        <v>0</v>
       </c>
       <c r="C83" s="68"/>
     </row>
-    <row r="84" spans="1:12">
-      <c r="A84" s="144" t="s">
+    <row r="84" spans="1:12" ht="17.25" customHeight="1">
+      <c r="A84" s="142" t="s">
+        <v>132</v>
+      </c>
+      <c r="B84" s="151">
+        <v>-75000</v>
+      </c>
+      <c r="C84" s="68"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="144" t="s">
         <v>38</v>
       </c>
-      <c r="B84" s="151">
-        <f>-B73</f>
-        <v>-1522444.65</v>
-      </c>
-      <c r="C84" s="68"/>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" s="143" t="s">
+      <c r="B85" s="151">
+        <f>-B74</f>
+        <v>-1528411.7</v>
+      </c>
+      <c r="C85" s="68"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="B85" s="62">
-        <f>-(B74)</f>
-        <v>0</v>
-      </c>
-      <c r="C85" s="68"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" s="11" t="s">
+      <c r="B86" s="62">
+        <f>-(B75)</f>
+        <v>0</v>
+      </c>
+      <c r="C86" s="68"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="104">
-        <f>SUM(B80:B85)</f>
-        <v>-109589.33000000077</v>
-      </c>
-      <c r="C86" s="129"/>
-    </row>
-    <row r="87" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B87" s="22"/>
-      <c r="C87" s="24"/>
-      <c r="D87" s="129"/>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" s="161" t="s">
+      <c r="B87" s="104">
+        <f>SUM(B81:B86)</f>
+        <v>1118920.2499999998</v>
+      </c>
+      <c r="C87" s="129"/>
+    </row>
+    <row r="88" spans="1:12" ht="34.5" customHeight="1">
+      <c r="B88" s="22"/>
+      <c r="C88" s="24"/>
+      <c r="D88" s="129"/>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="161" t="s">
         <v>46</v>
       </c>
-      <c r="B88" s="161"/>
-    </row>
-    <row r="89" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A89" s="161"/>
       <c r="B89" s="161"/>
     </row>
-    <row r="90" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A90" s="74"/>
-      <c r="B90" s="18"/>
+    <row r="90" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A90" s="161"/>
+      <c r="B90" s="161"/>
     </row>
     <row r="91" spans="1:12" ht="32.25" customHeight="1">
       <c r="A91" s="74"/>
       <c r="B91" s="18"/>
     </row>
-    <row r="92" spans="1:12">
-      <c r="A92" s="25" t="s">
+    <row r="92" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A92" s="74"/>
+      <c r="B92" s="18"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B92" s="75">
-        <f>SUM(B90:B91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12">
-      <c r="L93" s="4"/>
+      <c r="B93" s="75">
+        <f>SUM(B91:B92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="L94" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A88:B89"/>
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A89:B90"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2978,22 +2999,22 @@
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="105"/>
-      <c r="B1" s="166" t="str">
+      <c r="B1" s="170" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
       <c r="L1" s="106"/>
       <c r="M1" s="106"/>
       <c r="N1" s="106"/>
@@ -3002,16 +3023,16 @@
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
       <c r="A2" s="108"/>
-      <c r="B2" s="167"/>
-      <c r="C2" s="167"/>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
-      <c r="F2" s="167"/>
-      <c r="G2" s="167"/>
-      <c r="H2" s="167"/>
-      <c r="I2" s="167"/>
-      <c r="J2" s="167"/>
-      <c r="K2" s="167"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
       <c r="L2" s="109"/>
       <c r="M2" s="109" t="s">
         <v>4</v>
@@ -3028,16 +3049,16 @@
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
       <c r="A3" s="111"/>
-      <c r="B3" s="168"/>
-      <c r="C3" s="168"/>
-      <c r="D3" s="168"/>
-      <c r="E3" s="168"/>
-      <c r="F3" s="168"/>
-      <c r="G3" s="168"/>
-      <c r="H3" s="168"/>
-      <c r="I3" s="168"/>
-      <c r="J3" s="168"/>
-      <c r="K3" s="168"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
       <c r="L3" s="112"/>
       <c r="M3" s="112" t="s">
         <v>56</v>
@@ -3050,96 +3071,96 @@
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="179" t="s">
+      <c r="B4" s="182" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="180"/>
-      <c r="D4" s="180"/>
-      <c r="E4" s="180"/>
-      <c r="F4" s="180"/>
-      <c r="G4" s="180"/>
-      <c r="H4" s="180"/>
-      <c r="I4" s="180"/>
-      <c r="J4" s="180"/>
-      <c r="K4" s="180"/>
-      <c r="L4" s="180"/>
-      <c r="M4" s="180"/>
-      <c r="N4" s="180"/>
-      <c r="O4" s="180"/>
-      <c r="P4" s="181"/>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
+      <c r="H4" s="183"/>
+      <c r="I4" s="183"/>
+      <c r="J4" s="183"/>
+      <c r="K4" s="183"/>
+      <c r="L4" s="183"/>
+      <c r="M4" s="183"/>
+      <c r="N4" s="183"/>
+      <c r="O4" s="183"/>
+      <c r="P4" s="184"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="166" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="184" t="s">
+      <c r="B5" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="171" t="s">
+      <c r="C5" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="171" t="s">
+      <c r="D5" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="171" t="s">
+      <c r="E5" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="171" t="s">
+      <c r="F5" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="171" t="s">
+      <c r="G5" s="169" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="171" t="s">
+      <c r="H5" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="171" t="s">
+      <c r="I5" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="175" t="s">
+      <c r="J5" s="178" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="173" t="s">
+      <c r="K5" s="176" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="173" t="s">
+      <c r="L5" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="173" t="s">
+      <c r="M5" s="176" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="177" t="s">
+      <c r="N5" s="180" t="s">
         <v>51</v>
       </c>
       <c r="O5" s="94" t="s">
         <v>50</v>
       </c>
-      <c r="P5" s="169" t="s">
+      <c r="P5" s="173" t="s">
         <v>49</v>
       </c>
       <c r="S5" s="24"/>
       <c r="T5" s="22"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="183"/>
-      <c r="B6" s="184"/>
-      <c r="C6" s="171"/>
-      <c r="D6" s="171"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="171"/>
-      <c r="G6" s="171"/>
-      <c r="H6" s="171"/>
-      <c r="I6" s="172"/>
-      <c r="J6" s="176"/>
-      <c r="K6" s="174"/>
-      <c r="L6" s="173"/>
-      <c r="M6" s="174"/>
-      <c r="N6" s="178"/>
+      <c r="A6" s="167"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="175"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
+      <c r="H6" s="169"/>
+      <c r="I6" s="175"/>
+      <c r="J6" s="179"/>
+      <c r="K6" s="177"/>
+      <c r="L6" s="176"/>
+      <c r="M6" s="177"/>
+      <c r="N6" s="181"/>
       <c r="O6" s="29" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="P6" s="169"/>
+      <c r="P6" s="173"/>
       <c r="S6" s="22">
         <v>65160</v>
       </c>
@@ -3190,15 +3211,15 @@
         <v>178847.71777799999</v>
       </c>
       <c r="N7" s="41">
-        <v>148000</v>
+        <v>75000</v>
       </c>
       <c r="O7" s="42">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>5515105.0099999998</v>
+        <v>5442105.0099999998</v>
       </c>
       <c r="P7" s="43">
         <f t="shared" ref="P7:P23" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>5680558.0099999998</v>
+        <v>5605368.0099999998</v>
       </c>
       <c r="Q7" s="24">
         <v>0.01</v>
@@ -3232,17 +3253,20 @@
         <v>11.16</v>
       </c>
       <c r="G8" s="36">
-        <v>167834.02</v>
-      </c>
-      <c r="H8" s="152"/>
+        <v>172869.02</v>
+      </c>
+      <c r="H8" s="37">
+        <f>182538.14-H18</f>
+        <v>172869.02000000002</v>
+      </c>
       <c r="I8" s="38"/>
       <c r="J8" s="39">
         <f t="shared" ref="J8:J22" si="2">G8-H8</f>
-        <v>167834.02</v>
+        <v>0</v>
       </c>
       <c r="K8" s="39">
         <f t="shared" ref="K8:K22" si="3">IF(J8&gt;0,J8*3%,0)</f>
-        <v>5035.0205999999998</v>
+        <v>0</v>
       </c>
       <c r="L8" s="40">
         <f t="shared" ref="L8:L23" si="4">O$3*F8%</f>
@@ -3257,11 +3281,11 @@
       </c>
       <c r="O8" s="42">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>356657.02</v>
+        <v>183788.02</v>
       </c>
       <c r="P8" s="43">
         <f t="shared" si="0"/>
-        <v>367357.02</v>
+        <v>189302.02</v>
       </c>
       <c r="Q8" s="24">
         <f>Q7+0.01</f>
@@ -3301,7 +3325,7 @@
       <c r="G9" s="37">
         <v>114503.03</v>
       </c>
-      <c r="H9" s="152"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="38"/>
       <c r="J9" s="98">
         <f t="shared" si="2"/>
@@ -3367,7 +3391,7 @@
       <c r="G10" s="36">
         <v>310647.03999999998</v>
       </c>
-      <c r="H10" s="152">
+      <c r="H10" s="37">
         <f>157200+129937-H20</f>
         <v>265075.86</v>
       </c>
@@ -3436,7 +3460,7 @@
       <c r="G11" s="36">
         <v>175883.05</v>
       </c>
-      <c r="H11" s="152">
+      <c r="H11" s="37">
         <v>181159.05</v>
       </c>
       <c r="I11" s="38"/>
@@ -3504,7 +3528,7 @@
       <c r="G12" s="36">
         <v>71739.06</v>
       </c>
-      <c r="H12" s="152">
+      <c r="H12" s="37">
         <f>G12</f>
         <v>71739.06</v>
       </c>
@@ -3573,7 +3597,7 @@
       <c r="G13" s="36">
         <v>113468.07</v>
       </c>
-      <c r="H13" s="152">
+      <c r="H13" s="37">
         <f>G13</f>
         <v>113468.07</v>
       </c>
@@ -3643,7 +3667,7 @@
       <c r="G14" s="36">
         <v>175883.08</v>
       </c>
-      <c r="H14" s="152">
+      <c r="H14" s="37">
         <f>G14</f>
         <v>175883.08</v>
       </c>
@@ -3712,7 +3736,7 @@
       <c r="G15" s="37">
         <v>75188.09</v>
       </c>
-      <c r="H15" s="152">
+      <c r="H15" s="37">
         <f>G15*2</f>
         <v>150376.18</v>
       </c>
@@ -3780,7 +3804,7 @@
       <c r="G16" s="36">
         <v>153564.1</v>
       </c>
-      <c r="H16" s="152">
+      <c r="H16" s="37">
         <v>113468</v>
       </c>
       <c r="I16" s="38"/>
@@ -3849,7 +3873,7 @@
       <c r="G17" s="36">
         <v>195646.11</v>
       </c>
-      <c r="H17" s="152">
+      <c r="H17" s="37">
         <f>G17</f>
         <v>195646.11</v>
       </c>
@@ -3917,17 +3941,20 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G18" s="36">
-        <v>9387.1200000000008</v>
-      </c>
-      <c r="H18" s="152"/>
+        <v>9669.1200000000008</v>
+      </c>
+      <c r="H18" s="37">
+        <f>G18</f>
+        <v>9669.1200000000008</v>
+      </c>
       <c r="I18" s="38"/>
       <c r="J18" s="39">
         <f t="shared" si="2"/>
-        <v>9387.1200000000008</v>
+        <v>0</v>
       </c>
       <c r="K18" s="39">
         <f t="shared" si="3"/>
-        <v>281.61360000000002</v>
+        <v>0</v>
       </c>
       <c r="L18" s="40">
         <f t="shared" si="4"/>
@@ -3942,11 +3969,11 @@
       </c>
       <c r="O18" s="42">
         <f t="shared" si="6"/>
-        <v>19056.12</v>
+        <v>9387.1200000000008</v>
       </c>
       <c r="P18" s="43">
         <f t="shared" si="0"/>
-        <v>19628.12</v>
+        <v>9669.1200000000008</v>
       </c>
       <c r="Q18" s="24">
         <f t="shared" si="7"/>
@@ -3983,7 +4010,7 @@
       <c r="G19" s="36">
         <v>8564.1299999999992</v>
       </c>
-      <c r="H19" s="152">
+      <c r="H19" s="37">
         <v>8821.1299999999992</v>
       </c>
       <c r="I19" s="38"/>
@@ -4051,7 +4078,7 @@
       <c r="G20" s="36">
         <v>22061.14</v>
       </c>
-      <c r="H20" s="152">
+      <c r="H20" s="37">
         <f>G20</f>
         <v>22061.14</v>
       </c>
@@ -4118,7 +4145,7 @@
       <c r="G21" s="36">
         <v>8564.15</v>
       </c>
-      <c r="H21" s="152">
+      <c r="H21" s="37">
         <f>G21</f>
         <v>8564.15</v>
       </c>
@@ -4185,7 +4212,7 @@
       <c r="G22" s="36">
         <v>10046.16</v>
       </c>
-      <c r="H22" s="152">
+      <c r="H22" s="37">
         <f>G22</f>
         <v>10046.16</v>
       </c>
@@ -4280,11 +4307,11 @@
       </c>
       <c r="G24" s="27">
         <f>SUM(G7:G23)</f>
-        <v>6650121.3599999994</v>
+        <v>6655438.3599999994</v>
       </c>
       <c r="H24" s="30">
         <f>SUM(H7:H23)</f>
-        <v>1316307.9899999998</v>
+        <v>1498846.13</v>
       </c>
       <c r="I24" s="30">
         <f>SUM(I7:I23)</f>
@@ -4302,15 +4329,15 @@
       </c>
       <c r="N24" s="30">
         <f>SUM(N7:N23)</f>
-        <v>148000</v>
+        <v>75000</v>
       </c>
       <c r="O24" s="53">
         <f>SUM(O7:O22)</f>
-        <v>7291100.3599999994</v>
+        <v>7035562.3599999994</v>
       </c>
       <c r="P24" s="53">
         <f>SUM(P7:P22)</f>
-        <v>7509832.3599999994</v>
+        <v>7246628.3599999994</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="12.75" customHeight="1">
@@ -4320,99 +4347,94 @@
     </row>
     <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="D27" s="170" t="s">
+      <c r="D27" s="174" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="170"/>
-      <c r="F27" s="170"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="170"/>
-      <c r="I27" s="170"/>
-      <c r="J27" s="170"/>
-      <c r="K27" s="170"/>
-      <c r="L27" s="170"/>
-      <c r="M27" s="170"/>
-      <c r="N27" s="170"/>
-      <c r="O27" s="170"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="174"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="174"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="174"/>
+      <c r="L27" s="174"/>
+      <c r="M27" s="174"/>
+      <c r="N27" s="174"/>
+      <c r="O27" s="174"/>
       <c r="S27" s="22"/>
     </row>
     <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D28" s="170"/>
-      <c r="E28" s="170"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="170"/>
-      <c r="H28" s="170"/>
-      <c r="I28" s="170"/>
-      <c r="J28" s="170"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="170"/>
-      <c r="M28" s="170"/>
-      <c r="N28" s="170"/>
-      <c r="O28" s="170"/>
+      <c r="D28" s="174"/>
+      <c r="E28" s="174"/>
+      <c r="F28" s="174"/>
+      <c r="G28" s="174"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="174"/>
+      <c r="L28" s="174"/>
+      <c r="M28" s="174"/>
+      <c r="N28" s="174"/>
+      <c r="O28" s="174"/>
     </row>
     <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D29" s="170"/>
-      <c r="E29" s="170"/>
-      <c r="F29" s="170"/>
-      <c r="G29" s="170"/>
-      <c r="H29" s="170"/>
-      <c r="I29" s="170"/>
-      <c r="J29" s="170"/>
-      <c r="K29" s="170"/>
-      <c r="L29" s="170"/>
-      <c r="M29" s="170"/>
-      <c r="N29" s="170"/>
-      <c r="O29" s="170"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="174"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="174"/>
+      <c r="M29" s="174"/>
+      <c r="N29" s="174"/>
+      <c r="O29" s="174"/>
     </row>
     <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D30" s="170"/>
-      <c r="E30" s="170"/>
-      <c r="F30" s="170"/>
-      <c r="G30" s="170"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="170"/>
-      <c r="J30" s="170"/>
-      <c r="K30" s="170"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="170"/>
-      <c r="O30" s="170"/>
+      <c r="D30" s="174"/>
+      <c r="E30" s="174"/>
+      <c r="F30" s="174"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="174"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="174"/>
+      <c r="L30" s="174"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="174"/>
+      <c r="O30" s="174"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="170"/>
-      <c r="E31" s="170"/>
-      <c r="F31" s="170"/>
-      <c r="G31" s="170"/>
-      <c r="H31" s="170"/>
-      <c r="I31" s="170"/>
-      <c r="J31" s="170"/>
-      <c r="K31" s="170"/>
-      <c r="L31" s="170"/>
-      <c r="M31" s="170"/>
-      <c r="N31" s="170"/>
-      <c r="O31" s="170"/>
+      <c r="D31" s="174"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="174"/>
+      <c r="G31" s="174"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="174"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
+      <c r="L31" s="174"/>
+      <c r="M31" s="174"/>
+      <c r="N31" s="174"/>
+      <c r="O31" s="174"/>
     </row>
     <row r="32" spans="1:21" ht="65.25" customHeight="1">
-      <c r="D32" s="170"/>
-      <c r="E32" s="170"/>
-      <c r="F32" s="170"/>
-      <c r="G32" s="170"/>
-      <c r="H32" s="170"/>
-      <c r="I32" s="170"/>
-      <c r="J32" s="170"/>
-      <c r="K32" s="170"/>
-      <c r="L32" s="170"/>
-      <c r="M32" s="170"/>
-      <c r="N32" s="170"/>
-      <c r="O32" s="170"/>
+      <c r="D32" s="174"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="174"/>
+      <c r="G32" s="174"/>
+      <c r="H32" s="174"/>
+      <c r="I32" s="174"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="174"/>
+      <c r="L32" s="174"/>
+      <c r="M32" s="174"/>
+      <c r="N32" s="174"/>
+      <c r="O32" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D27:O32"/>
@@ -4426,6 +4448,11 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
@@ -4439,7 +4466,7 @@
   <sheetData>
     <row r="3" spans="3:3">
       <c r="C3" s="148" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
